--- a/correlations/multiple_regressions/multiple_regressions_spring.xlsx
+++ b/correlations/multiple_regressions/multiple_regressions_spring.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\correlations\multiple_regressions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\correlations\multiple_regressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E4B14C-53AE-4D2F-8E1A-EA4B6ECE36A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00DA5A9-6349-462E-9F81-3F69F30A6FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20250" yWindow="2850" windowWidth="18900" windowHeight="10965" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="69">
   <si>
     <t>SSC (mg/L)</t>
   </si>
@@ -558,7 +558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -837,6 +837,18 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1712,6 +1724,1044 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
+              <a:t> to E integral</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17906646573955362"/>
+          <c:y val="2.4822690414793021E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>downstream!$B$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Aich SSC </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.36721341650475509"/>
+                  <c:y val="0.10342811315252261"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>downstream!$B$38:$B$53</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>9.4513218106104094E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.2663094228711902E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.8732929175135894E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1.9463558010346702E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.10415722716452799</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.66251429291673E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.0894558490112708E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.0373962034653699E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>downstream!$F$38:$F$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="2" formatCode="0.000">
+                  <c:v>1.9432258375425799</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.000">
+                  <c:v>2.3768784113539301</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.000">
+                  <c:v>70.349925179505803</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.000">
+                  <c:v>5.4523947827090398</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>33.895949402833203</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.000">
+                  <c:v>32.177431699139497</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.000">
+                  <c:v>31.253302872972</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.000">
+                  <c:v>42.7547044117564</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.000">
+                  <c:v>175.86248095131899</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0.000">
+                  <c:v>52.638565780695899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-ED3B-49A5-AFA6-13EA4B1ED9CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>downstream!$C$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Aich DOC </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.29929429064677021"/>
+                  <c:y val="-0.26846554076328794"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>downstream!$C$38:$C$53</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>3.4332675043980999E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.8668980226143202E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.20306787922476E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.7386597361713599E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.8615745110634201E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.4113621235337297E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-8.0536265843332393E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.7450804091866201E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>downstream!$F$38:$F$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="2" formatCode="0.000">
+                  <c:v>1.9432258375425799</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.000">
+                  <c:v>2.3768784113539301</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.000">
+                  <c:v>70.349925179505803</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.000">
+                  <c:v>5.4523947827090398</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>33.895949402833203</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.000">
+                  <c:v>32.177431699139497</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.000">
+                  <c:v>31.253302872972</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.000">
+                  <c:v>42.7547044117564</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.000">
+                  <c:v>175.86248095131899</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0.000">
+                  <c:v>52.638565780695899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-ED3B-49A5-AFA6-13EA4B1ED9CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>downstream!$D$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Aich Turbidity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="6.6765177080137711E-2"/>
+                  <c:y val="-0.24872849227179936"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>downstream!$D$38:$D$53</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>5.1856335362832198E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.103368750113241</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.11077055296162799</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0650915621547401E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2.2683422982125001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.15621819275209001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.15071577677020101</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.5397551503622099E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.9883057908481996E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.8645648239850305E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.17832892113485599</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.1496979213356301E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.101236914763633</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.107400232693555</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>downstream!$F$38:$F$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="2" formatCode="0.000">
+                  <c:v>1.9432258375425799</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.000">
+                  <c:v>2.3768784113539301</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.000">
+                  <c:v>70.349925179505803</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.000">
+                  <c:v>5.4523947827090398</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>33.895949402833203</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.000">
+                  <c:v>32.177431699139497</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.000">
+                  <c:v>31.253302872972</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.000">
+                  <c:v>42.7547044117564</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.000">
+                  <c:v>175.86248095131899</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0.000">
+                  <c:v>52.638565780695899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-ED3B-49A5-AFA6-13EA4B1ED9CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>downstream!$E$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Aich fDOM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.14486211950778885"/>
+                  <c:y val="-0.18315398075240594"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>downstream!$E$38:$E$53</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>1.3430417175947699E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.61778645652975E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.7834846370905402E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.4581353214806597E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.1895687016862502E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.95836818188689E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-5.4892758010415703E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.8641812543785899E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.32778322661357E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-6.0975544853349099E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.2081062239471598E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1.77749404385871E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.08855730575289E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-5.3081166180475401E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>downstream!$F$38:$F$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="2" formatCode="0.000">
+                  <c:v>1.9432258375425799</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.000">
+                  <c:v>2.3768784113539301</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.000">
+                  <c:v>70.349925179505803</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.000">
+                  <c:v>5.4523947827090398</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>33.895949402833203</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.000">
+                  <c:v>32.177431699139497</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.000">
+                  <c:v>31.253302872972</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.000">
+                  <c:v>42.7547044117564</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.000">
+                  <c:v>175.86248095131899</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0.000">
+                  <c:v>52.638565780695899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-ED3B-49A5-AFA6-13EA4B1ED9CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="892378239"/>
+        <c:axId val="892384479"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="892378239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="892384479"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="892384479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="892378239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="7"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Aich HI</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
               <a:t> to </a:t>
             </a:r>
             <a:r>
@@ -2727,7 +3777,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3765,7 +4815,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4811,7 +5861,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5492,7 +6542,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5936,690 +6986,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-DEF4-4A2F-939C-8935D033F4BB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="892378239"/>
-        <c:axId val="892384479"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="892378239"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="low"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="892384479"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="892384479"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="low"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="892378239"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:legendEntry>
-        <c:idx val="2"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="3"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Aich HI</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> to E integral</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.17906646573955362"/>
-          <c:y val="2.4822690414793021E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>upstream!$B$38</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Aich SSC </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.3389400433588905"/>
-                  <c:y val="-0.26379671291088613"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>upstream!$B$39:$B$52</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>2.4947102971666898E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9.6293174744729593E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.14608753400636901</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.27691539373017E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6.7576112725014403E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.0119527368219401E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.5646344187588998E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.47909285306715E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.5842816756479302E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2.0282132481243099E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>3.6679485231980898E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>7.7980025652416296E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>upstream!$F$39:$F$52</c:f>
-              <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="2">
-                  <c:v>1.9432258375425799</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.3768784113539301</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>70.349925179505803</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5.4523947827090398</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>33.895949402833203</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>32.177431699139497</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>31.253302872972</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>42.7547044117564</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>175.86248095131899</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>52.638565780695899</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2E3E-4133-8EB0-E9EF889A8F58}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>upstream!$D$38</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Aich Turbidity</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="6.6765177080137711E-2"/>
-                  <c:y val="-0.24872849227179936"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent3">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>upstream!$D$39:$D$52</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>8.4573685986466099E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.198594884621278</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.8212961854365706E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.9611646415268197E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.107447815904682</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.39411883766970102</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9.0698601563059603E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>9.9852529707758195E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>5.5815481283492403E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9.5391388976058394E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>9.9540545016305104E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.115227328160236</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.157732693122626</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.121156039239802</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>upstream!$F$39:$F$52</c:f>
-              <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="2">
-                  <c:v>1.9432258375425799</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.3768784113539301</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>70.349925179505803</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5.4523947827090398</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>33.895949402833203</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>32.177431699139497</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>31.253302872972</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>42.7547044117564</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>175.86248095131899</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>52.638565780695899</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-2E3E-4133-8EB0-E9EF889A8F58}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6888,6 +7254,690 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
+              <a:t> to E integral</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17906646573955362"/>
+          <c:y val="2.4822690414793021E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>upstream!$B$38</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Aich SSC </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.3389400433588905"/>
+                  <c:y val="-0.26379671291088613"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>upstream!$B$39:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>2.4947102971666898E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.6293174744729593E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.14608753400636901</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.27691539373017E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.7576112725014403E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0119527368219401E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.5646344187588998E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.47909285306715E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.5842816756479302E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.0282132481243099E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.6679485231980898E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.7980025652416296E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>upstream!$F$39:$F$52</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="2">
+                  <c:v>1.9432258375425799</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.3768784113539301</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70.349925179505803</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4523947827090398</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>33.895949402833203</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32.177431699139497</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>31.253302872972</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>42.7547044117564</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>175.86248095131899</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>52.638565780695899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2E3E-4133-8EB0-E9EF889A8F58}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>upstream!$D$38</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Aich Turbidity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="6.6765177080137711E-2"/>
+                  <c:y val="-0.24872849227179936"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>upstream!$D$39:$D$52</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>8.4573685986466099E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.198594884621278</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.8212961854365706E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.9611646415268197E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.107447815904682</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.39411883766970102</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.0698601563059603E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.9852529707758195E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.5815481283492403E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.5391388976058394E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.9540545016305104E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.115227328160236</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.157732693122626</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.121156039239802</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>upstream!$F$39:$F$52</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="2">
+                  <c:v>1.9432258375425799</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.3768784113539301</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70.349925179505803</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4523947827090398</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>33.895949402833203</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32.177431699139497</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>31.253302872972</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>42.7547044117564</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>175.86248095131899</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>52.638565780695899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-2E3E-4133-8EB0-E9EF889A8F58}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="892378239"/>
+        <c:axId val="892384479"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="892378239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="892384479"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="892384479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="892378239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Aich HI</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
               <a:t> to </a:t>
             </a:r>
             <a:r>
@@ -7549,7 +8599,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8233,7 +9283,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -13006,6 +14056,427 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="9.1318833455630039E-3"/>
+                  <c:y val="-0.15073743006323498"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>all!$Y$8:$Y$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>1.3430417175947699E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.61778645652975E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.7834846370905402E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.4581353214806597E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.1895687016862502E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.95836818188689E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-5.4892758010415703E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.8641812543785899E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.32778322661357E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-6.0975544853349099E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.2081062239471598E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1.77749404385871E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.08855730575289E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-5.3081166180475401E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>all!$Z$8:$Z$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>-9.3763935417501706E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-5.2796335197095298E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-5.9125313303963402E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.1714957549384597E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.3340759088016003E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.1354925056258001E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.28463650723553102</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-7.3287190867590401E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.10941628444022999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-8.4675321487204705E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-3.2911415817637998E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-4.46763074582908E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.53118918462132E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.17920927988478999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FAB1-435B-A848-8BFD33153008}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="525947216"/>
+        <c:axId val="220125040"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="525947216"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="220125040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="220125040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="525947216"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:tx>
         <c:rich>
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
@@ -13655,7 +15126,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -14448,1044 +15919,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000007-2925-4FE1-97EC-D92264973B19}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="892378239"/>
-        <c:axId val="892384479"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="892378239"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="low"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="892384479"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="892384479"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="low"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="892378239"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:legendEntry>
-        <c:idx val="4"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="5"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="6"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="7"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Aich HI</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> to E integral</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.17906646573955362"/>
-          <c:y val="2.4822690414793021E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>downstream!$B$37</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Aich SSC </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.36721341650475509"/>
-                  <c:y val="0.10342811315252261"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>downstream!$B$38:$B$53</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="16"/>
-                <c:pt idx="0">
-                  <c:v>9.4513218106104094E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.2663094228711902E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>8.8732929175135894E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-1.9463558010346702E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.10415722716452799</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.66251429291673E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9.0894558490112708E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.0373962034653699E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>downstream!$F$38:$F$53</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
-                <c:pt idx="2" formatCode="0.000">
-                  <c:v>1.9432258375425799</c:v>
-                </c:pt>
-                <c:pt idx="3" formatCode="0.000">
-                  <c:v>2.3768784113539301</c:v>
-                </c:pt>
-                <c:pt idx="4" formatCode="0.000">
-                  <c:v>70.349925179505803</c:v>
-                </c:pt>
-                <c:pt idx="5" formatCode="0.000">
-                  <c:v>5.4523947827090398</c:v>
-                </c:pt>
-                <c:pt idx="7" formatCode="0.000">
-                  <c:v>33.895949402833203</c:v>
-                </c:pt>
-                <c:pt idx="8" formatCode="0.000">
-                  <c:v>32.177431699139497</c:v>
-                </c:pt>
-                <c:pt idx="9" formatCode="0.000">
-                  <c:v>31.253302872972</c:v>
-                </c:pt>
-                <c:pt idx="11" formatCode="0.000">
-                  <c:v>42.7547044117564</c:v>
-                </c:pt>
-                <c:pt idx="12" formatCode="0.000">
-                  <c:v>175.86248095131899</c:v>
-                </c:pt>
-                <c:pt idx="13" formatCode="0.000">
-                  <c:v>52.638565780695899</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-ED3B-49A5-AFA6-13EA4B1ED9CB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>downstream!$C$37</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Aich DOC </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.29929429064677021"/>
-                  <c:y val="-0.26846554076328794"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>downstream!$C$38:$C$53</c:f>
-              <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="16"/>
-                <c:pt idx="0">
-                  <c:v>3.4332675043980999E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.8668980226143202E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.20306787922476E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.7386597361713599E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.8615745110634201E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.4113621235337297E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-8.0536265843332393E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.7450804091866201E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>downstream!$F$38:$F$53</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
-                <c:pt idx="2" formatCode="0.000">
-                  <c:v>1.9432258375425799</c:v>
-                </c:pt>
-                <c:pt idx="3" formatCode="0.000">
-                  <c:v>2.3768784113539301</c:v>
-                </c:pt>
-                <c:pt idx="4" formatCode="0.000">
-                  <c:v>70.349925179505803</c:v>
-                </c:pt>
-                <c:pt idx="5" formatCode="0.000">
-                  <c:v>5.4523947827090398</c:v>
-                </c:pt>
-                <c:pt idx="7" formatCode="0.000">
-                  <c:v>33.895949402833203</c:v>
-                </c:pt>
-                <c:pt idx="8" formatCode="0.000">
-                  <c:v>32.177431699139497</c:v>
-                </c:pt>
-                <c:pt idx="9" formatCode="0.000">
-                  <c:v>31.253302872972</c:v>
-                </c:pt>
-                <c:pt idx="11" formatCode="0.000">
-                  <c:v>42.7547044117564</c:v>
-                </c:pt>
-                <c:pt idx="12" formatCode="0.000">
-                  <c:v>175.86248095131899</c:v>
-                </c:pt>
-                <c:pt idx="13" formatCode="0.000">
-                  <c:v>52.638565780695899</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-ED3B-49A5-AFA6-13EA4B1ED9CB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>downstream!$D$37</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Aich Turbidity</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="6.6765177080137711E-2"/>
-                  <c:y val="-0.24872849227179936"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent3">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>downstream!$D$38:$D$53</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="16"/>
-                <c:pt idx="0">
-                  <c:v>5.1856335362832198E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.103368750113241</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.11077055296162799</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.0650915621547401E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-2.2683422982125001E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.15621819275209001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.15071577677020101</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>5.5397551503622099E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>6.9883057908481996E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7.8645648239850305E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.17832892113485599</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2.1496979213356301E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.101236914763633</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.107400232693555</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>downstream!$F$38:$F$53</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
-                <c:pt idx="2" formatCode="0.000">
-                  <c:v>1.9432258375425799</c:v>
-                </c:pt>
-                <c:pt idx="3" formatCode="0.000">
-                  <c:v>2.3768784113539301</c:v>
-                </c:pt>
-                <c:pt idx="4" formatCode="0.000">
-                  <c:v>70.349925179505803</c:v>
-                </c:pt>
-                <c:pt idx="5" formatCode="0.000">
-                  <c:v>5.4523947827090398</c:v>
-                </c:pt>
-                <c:pt idx="7" formatCode="0.000">
-                  <c:v>33.895949402833203</c:v>
-                </c:pt>
-                <c:pt idx="8" formatCode="0.000">
-                  <c:v>32.177431699139497</c:v>
-                </c:pt>
-                <c:pt idx="9" formatCode="0.000">
-                  <c:v>31.253302872972</c:v>
-                </c:pt>
-                <c:pt idx="11" formatCode="0.000">
-                  <c:v>42.7547044117564</c:v>
-                </c:pt>
-                <c:pt idx="12" formatCode="0.000">
-                  <c:v>175.86248095131899</c:v>
-                </c:pt>
-                <c:pt idx="13" formatCode="0.000">
-                  <c:v>52.638565780695899</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-ED3B-49A5-AFA6-13EA4B1ED9CB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>downstream!$E$37</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Aich fDOM</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.14486211950778885"/>
-                  <c:y val="-0.18315398075240594"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>downstream!$E$38:$E$53</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="16"/>
-                <c:pt idx="0">
-                  <c:v>1.3430417175947699E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-1.61778645652975E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-3.7834846370905402E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.4581353214806597E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.1895687016862502E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.95836818188689E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-5.4892758010415703E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8.8641812543785899E-3</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.32778322661357E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-6.0975544853349099E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4.2081062239471598E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-1.77749404385871E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>3.08855730575289E-3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-5.3081166180475401E-3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>downstream!$F$38:$F$53</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
-                <c:pt idx="2" formatCode="0.000">
-                  <c:v>1.9432258375425799</c:v>
-                </c:pt>
-                <c:pt idx="3" formatCode="0.000">
-                  <c:v>2.3768784113539301</c:v>
-                </c:pt>
-                <c:pt idx="4" formatCode="0.000">
-                  <c:v>70.349925179505803</c:v>
-                </c:pt>
-                <c:pt idx="5" formatCode="0.000">
-                  <c:v>5.4523947827090398</c:v>
-                </c:pt>
-                <c:pt idx="7" formatCode="0.000">
-                  <c:v>33.895949402833203</c:v>
-                </c:pt>
-                <c:pt idx="8" formatCode="0.000">
-                  <c:v>32.177431699139497</c:v>
-                </c:pt>
-                <c:pt idx="9" formatCode="0.000">
-                  <c:v>31.253302872972</c:v>
-                </c:pt>
-                <c:pt idx="11" formatCode="0.000">
-                  <c:v>42.7547044117564</c:v>
-                </c:pt>
-                <c:pt idx="12" formatCode="0.000">
-                  <c:v>175.86248095131899</c:v>
-                </c:pt>
-                <c:pt idx="13" formatCode="0.000">
-                  <c:v>52.638565780695899</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-ED3B-49A5-AFA6-13EA4B1ED9CB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -16123,6 +16556,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors19.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -21603,6 +22076,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style19.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -25954,6 +26943,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>936172</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>43543</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>531495</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>25582</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC902D05-368B-68AA-BEFB-3943B9031E12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -26719,7 +27744,7 @@
     <col min="30" max="30" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -26733,7 +27758,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -26783,7 +27808,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -26829,7 +27854,7 @@
         <v>1.3430417175947699E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -26879,7 +27904,7 @@
         <v>-1.61778645652975E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -26917,7 +27942,7 @@
         <v>-3.7834846370905402E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -26955,7 +27980,7 @@
         <v>6.4581353214806597E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
@@ -26993,7 +28018,7 @@
         <v>6.1895687016862502E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -27042,8 +28067,17 @@
       <c r="S8" s="5">
         <v>2.95836818188689E-2</v>
       </c>
+      <c r="X8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>1.3430417175947699E-2</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>-9.3763935417501706E-2</v>
+      </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
@@ -27092,8 +28126,17 @@
       <c r="S9" s="6">
         <v>-5.4892758010415703E-2</v>
       </c>
+      <c r="X9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>-1.61778645652975E-2</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>-5.2796335197095298E-2</v>
+      </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -27142,8 +28185,17 @@
       <c r="S10" s="5">
         <v>8.8641812543785899E-3</v>
       </c>
+      <c r="X10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>-3.7834846370905402E-3</v>
+      </c>
+      <c r="Z10" s="10">
+        <v>-5.9125313303963402E-2</v>
+      </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -27192,8 +28244,17 @@
       <c r="S11" s="5">
         <v>1.32778322661357E-2</v>
       </c>
+      <c r="X11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>6.4581353214806597E-2</v>
+      </c>
+      <c r="Z11" s="10">
+        <v>-4.1714957549384597E-2</v>
+      </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
@@ -27242,8 +28303,17 @@
       <c r="S12" s="6">
         <v>-6.0975544853349099E-2</v>
       </c>
+      <c r="X12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>6.1895687016862502E-2</v>
+      </c>
+      <c r="Z12" s="9">
+        <v>7.3340759088016003E-2</v>
+      </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
@@ -27280,8 +28350,17 @@
       <c r="S13" s="5">
         <v>4.2081062239471598E-2</v>
       </c>
+      <c r="X13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y13" s="126">
+        <v>2.95836818188689E-2</v>
+      </c>
+      <c r="Z13" s="127">
+        <v>7.1354925056258001E-3</v>
+      </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
@@ -27318,8 +28397,17 @@
       <c r="S14" s="6">
         <v>-1.77749404385871E-2</v>
       </c>
+      <c r="X14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>-5.4892758010415703E-2</v>
+      </c>
+      <c r="Z14" s="10">
+        <v>-0.28463650723553102</v>
+      </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
@@ -27368,8 +28456,17 @@
       <c r="S15" s="5">
         <v>3.08855730575289E-3</v>
       </c>
+      <c r="X15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y15" s="126">
+        <v>8.8641812543785899E-3</v>
+      </c>
+      <c r="Z15" s="129">
+        <v>-7.3287190867590401E-3</v>
+      </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
@@ -27406,8 +28503,17 @@
       <c r="S16" s="6">
         <v>-5.3081166180475401E-3</v>
       </c>
+      <c r="X16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y16" s="126">
+        <v>1.32778322661357E-2</v>
+      </c>
+      <c r="Z16" s="127">
+        <v>0.10941628444022999</v>
+      </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
@@ -27456,8 +28562,17 @@
       <c r="S17" s="10">
         <v>-9.3763935417501706E-2</v>
       </c>
+      <c r="X17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y17" s="128">
+        <v>-6.0975544853349099E-2</v>
+      </c>
+      <c r="Z17" s="129">
+        <v>-8.4675321487204705E-2</v>
+      </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>6</v>
       </c>
@@ -27506,8 +28621,17 @@
       <c r="S18" s="10">
         <v>-5.2796335197095298E-2</v>
       </c>
+      <c r="X18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y18" s="5">
+        <v>4.2081062239471598E-2</v>
+      </c>
+      <c r="Z18" s="10">
+        <v>-3.2911415817637998E-2</v>
+      </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>7</v>
       </c>
@@ -27556,8 +28680,17 @@
       <c r="S19" s="10">
         <v>-5.9125313303963402E-2</v>
       </c>
+      <c r="X19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y19" s="128">
+        <v>-1.77749404385871E-2</v>
+      </c>
+      <c r="Z19" s="129">
+        <v>-4.46763074582908E-2</v>
+      </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>8</v>
       </c>
@@ -27594,8 +28727,17 @@
       <c r="S20" s="10">
         <v>-4.1714957549384597E-2</v>
       </c>
+      <c r="X20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y20" s="126">
+        <v>3.08855730575289E-3</v>
+      </c>
+      <c r="Z20" s="129">
+        <v>-1.53118918462132E-3</v>
+      </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
@@ -27638,8 +28780,17 @@
       <c r="S21" s="9">
         <v>7.3340759088016003E-2</v>
       </c>
+      <c r="X21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y21" s="128">
+        <v>-5.3081166180475401E-3</v>
+      </c>
+      <c r="Z21" s="129">
+        <v>-0.17920927988478999</v>
+      </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>10</v>
       </c>
@@ -27689,7 +28840,7 @@
         <v>7.1354925056258001E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>11</v>
       </c>
@@ -27739,7 +28890,7 @@
         <v>-0.28463650723553102</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>12</v>
       </c>
@@ -27789,7 +28940,7 @@
         <v>-7.3287190867590401E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>13</v>
       </c>
@@ -27839,7 +28990,7 @@
         <v>0.10941628444022999</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>14</v>
       </c>
@@ -27889,7 +29040,7 @@
         <v>-8.4675321487204705E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>15</v>
       </c>
@@ -27937,7 +29088,7 @@
         <v>-3.2911415817637998E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>16</v>
       </c>
@@ -27987,7 +29138,7 @@
         <v>-4.46763074582908E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>17</v>
       </c>
@@ -28037,7 +29188,7 @@
         <v>-1.53118918462132E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>18</v>
       </c>
